--- a/5/search/strategy_visualization/strategy_summary.xlsx
+++ b/5/search/strategy_visualization/strategy_summary.xlsx
@@ -457,19 +457,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20.5899999999997</v>
+        <v>20.87999999999976</v>
       </c>
       <c r="B2" t="n">
-        <v>6.41</v>
+        <v>9.48</v>
       </c>
       <c r="C2" t="n">
-        <v>7.569999999999839</v>
+        <v>7.649999999999837</v>
       </c>
       <c r="D2" t="n">
-        <v>6.609999999999859</v>
+        <v>3.749999999999922</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/strategy_visualization/strategy_summary.xlsx
+++ b/5/search/strategy_visualization/strategy_summary.xlsx
@@ -457,16 +457,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20.87999999999976</v>
+        <v>20.83999999999969</v>
       </c>
       <c r="B2" t="n">
-        <v>9.48</v>
+        <v>6.41</v>
       </c>
       <c r="C2" t="n">
-        <v>7.649999999999837</v>
+        <v>7.629999999999837</v>
       </c>
       <c r="D2" t="n">
-        <v>3.749999999999922</v>
+        <v>6.799999999999855</v>
       </c>
       <c r="E2" t="n">
         <v>7</v>
